--- a/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/BANG_BOC_TACH_TOAN_BO_BAN_VE_CAU_KM19.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/03_KINH_TE_QS_DU_TOAN_THANH_TOAN/BANG_BOC_TACH_TOAN_BO_BAN_VE_CAU_KM19.xlsx
@@ -122,7 +122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -158,11 +158,104 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -222,6 +315,13 @@
     <xf numFmtId="4" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -296,6 +396,166 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12858750" cy="7505700"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12858750" cy="7505700"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12858750" cy="7419975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12858750" cy="7915275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12858750" cy="8572500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12858750" cy="8572500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -587,8 +847,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:S40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="102" customWidth="1" min="2" max="2"/>
@@ -611,7 +871,6 @@
     <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -626,102 +885,107 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>TỔNG BÊ TÔNG TOÀN CẦU</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="26" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>TỔNG CỐT THÉP THƯỜNG</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>CÁP DƯL 15.2MM KÉO TRƯỚC</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="26" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>CỌC KHOAN NHỒI D1200MM</t>
         </is>
       </c>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="26" t="n"/>
       <c r="N5" s="3" t="inlineStr">
         <is>
           <t>TỔNG DIỆN TÍCH VÁN KHUÔN</t>
         </is>
       </c>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="26" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>VẬT LIỆU HẠT ĐẮP LÒNG MỐ</t>
         </is>
       </c>
-      <c r="R5" s="4" t="n"/>
-      <c r="S5" s="4" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="26" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="5">
         <f>'06_MASTER_BOQ_TIEN_LUONG'!G45</f>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+        <v/>
+      </c>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="28" t="n"/>
       <c r="E6" s="5">
         <f>'06_MASTER_BOQ_TIEN_LUONG'!G46</f>
-      </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+        <v/>
+      </c>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="28" t="n"/>
       <c r="H6" s="5">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G8</f>
-      </c>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
+        <f>'01_DIEN_GIAI_SUPER_T'!K16</f>
+        <v/>
+      </c>
+      <c r="I6" s="27" t="n"/>
+      <c r="J6" s="28" t="n"/>
       <c r="K6" s="5">
-        <f>'02_DIEN_GIAI_HA_BO'!J52</f>
-      </c>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
+        <f>'02_DIEN_GIAI_HA_BO'!K45</f>
+        <v/>
+      </c>
+      <c r="L6" s="27" t="n"/>
+      <c r="M6" s="28" t="n"/>
       <c r="N6" s="5">
         <f>'06_MASTER_BOQ_TIEN_LUONG'!G47</f>
-      </c>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
+        <v/>
+      </c>
+      <c r="O6" s="27" t="n"/>
+      <c r="P6" s="28" t="n"/>
       <c r="Q6" s="5">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G34</f>
-      </c>
-      <c r="R6" s="4" t="n"/>
-      <c r="S6" s="4" t="n"/>
+        <f>'04_DIEN_GIAI_DUONG_TU_NON'!K34</f>
+        <v/>
+      </c>
+      <c r="R6" s="27" t="n"/>
+      <c r="S6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
-      <c r="S7" s="4" t="n"/>
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="30" t="n"/>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="29" t="n"/>
+      <c r="I7" s="30" t="n"/>
+      <c r="J7" s="31" t="n"/>
+      <c r="K7" s="29" t="n"/>
+      <c r="L7" s="30" t="n"/>
+      <c r="M7" s="31" t="n"/>
+      <c r="N7" s="29" t="n"/>
+      <c r="O7" s="30" t="n"/>
+      <c r="P7" s="31" t="n"/>
+      <c r="Q7" s="29" t="n"/>
+      <c r="R7" s="30" t="n"/>
+      <c r="S7" s="31" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
@@ -729,45 +993,44 @@
           <t>m³ (C10 đến C45)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="26" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Tấn (CB400-V / CB240-T)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="26" t="n"/>
       <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Tấn (44 tao/dầm x 15 phiến)</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="26" t="n"/>
       <c r="K8" s="6" t="inlineStr">
         <is>
           <t>Mét (26 cọc đại trà)</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
+      <c r="L8" s="25" t="n"/>
+      <c r="M8" s="26" t="n"/>
       <c r="N8" s="6" t="inlineStr">
         <is>
           <t>m² (Dầm, Mố, Trụ, Phụ trợ)</t>
         </is>
       </c>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
+      <c r="O8" s="25" t="n"/>
+      <c r="P8" s="26" t="n"/>
       <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>m³ (Hạt đầm chặt K98)</t>
         </is>
       </c>
-      <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
-    </row>
-    <row r="9"/>
+      <c r="R8" s="25" t="n"/>
+      <c r="S8" s="26" t="n"/>
+    </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -828,14 +1091,14 @@
           <t>I. KẾT CẤU PHẦN TRÊN (SUPERSTRUCTURE)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="26" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="11" t="inlineStr">
@@ -862,16 +1125,20 @@
         <v>434.55</v>
       </c>
       <c r="G13" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G7</f>
+        <f>'01_DIEN_GIAI_SUPER_T'!K11</f>
+        <v/>
       </c>
       <c r="H13" s="13">
         <f>G13-F13</f>
+        <v/>
       </c>
       <c r="I13" s="14">
         <f>IF(F13=0,0,H13/F13)</f>
+        <v/>
       </c>
       <c r="J13" s="15">
         <f>IF(ABS(I13)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -899,16 +1166,20 @@
         <v>29911.2</v>
       </c>
       <c r="G14" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G8*1000</f>
+        <f>'01_DIEN_GIAI_SUPER_T'!K13</f>
+        <v/>
       </c>
       <c r="H14" s="13">
         <f>G14-F14</f>
+        <v/>
       </c>
       <c r="I14" s="14">
         <f>IF(F14=0,0,H14/F14)</f>
+        <v/>
       </c>
       <c r="J14" s="15">
         <f>IF(ABS(I14)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -936,16 +1207,20 @@
         <v>89668.81</v>
       </c>
       <c r="G15" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G9*1000</f>
+        <f>'01_DIEN_GIAI_SUPER_T'!K18+'01_DIEN_GIAI_SUPER_T'!K19</f>
+        <v/>
       </c>
       <c r="H15" s="13">
         <f>G15-F15</f>
+        <v/>
       </c>
       <c r="I15" s="14">
         <f>IF(F15=0,0,H15/F15)</f>
+        <v/>
       </c>
       <c r="J15" s="15">
         <f>IF(ABS(I15)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -973,16 +1248,20 @@
         <v>5098.77</v>
       </c>
       <c r="G16" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G10</f>
+        <f>'01_DIEN_GIAI_SUPER_T'!K27</f>
+        <v/>
       </c>
       <c r="H16" s="13">
         <f>G16-F16</f>
+        <v/>
       </c>
       <c r="I16" s="14">
         <f>IF(F16=0,0,H16/F16)</f>
+        <v/>
       </c>
       <c r="J16" s="15">
         <f>IF(ABS(I16)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1010,16 +1289,20 @@
         <v>19.38</v>
       </c>
       <c r="G17" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G11</f>
+        <f>'01_DIEN_GIAI_SUPER_T'!K34</f>
+        <v/>
       </c>
       <c r="H17" s="13">
         <f>G17-F17</f>
+        <v/>
       </c>
       <c r="I17" s="14">
         <f>IF(F17=0,0,H17/F17)</f>
+        <v/>
       </c>
       <c r="J17" s="15">
         <f>IF(ABS(I17)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1047,16 +1330,20 @@
         <v>327.33</v>
       </c>
       <c r="G18" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G12</f>
+        <f>'01_DIEN_GIAI_SUPER_T'!K43</f>
+        <v/>
       </c>
       <c r="H18" s="13">
         <f>G18-F18</f>
+        <v/>
       </c>
       <c r="I18" s="14">
         <f>IF(F18=0,0,H18/F18)</f>
+        <v/>
       </c>
       <c r="J18" s="15">
         <f>IF(ABS(I18)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1084,16 +1371,20 @@
         <v>88357.50999999999</v>
       </c>
       <c r="G19" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G13*1000</f>
+        <f>'01_DIEN_GIAI_SUPER_T'!K31+'01_DIEN_GIAI_SUPER_T'!K41</f>
+        <v/>
       </c>
       <c r="H19" s="13">
         <f>G19-F19</f>
+        <v/>
       </c>
       <c r="I19" s="14">
         <f>IF(F19=0,0,H19/F19)</f>
+        <v/>
       </c>
       <c r="J19" s="15">
         <f>IF(ABS(I19)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1121,16 +1412,20 @@
         <v>13.23</v>
       </c>
       <c r="G20" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G14</f>
+        <f>'01_DIEN_GIAI_SUPER_T'!K48</f>
+        <v/>
       </c>
       <c r="H20" s="13">
         <f>G20-F20</f>
+        <v/>
       </c>
       <c r="I20" s="14">
         <f>IF(F20=0,0,H20/F20)</f>
+        <v/>
       </c>
       <c r="J20" s="15">
         <f>IF(ABS(I20)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1158,16 +1453,20 @@
         <v>1380.39</v>
       </c>
       <c r="G21" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G15</f>
+        <f>'01_DIEN_GIAI_SUPER_T'!K53</f>
+        <v/>
       </c>
       <c r="H21" s="13">
         <f>G21-F21</f>
+        <v/>
       </c>
       <c r="I21" s="14">
         <f>IF(F21=0,0,H21/F21)</f>
+        <v/>
       </c>
       <c r="J21" s="15">
         <f>IF(ABS(I21)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1176,14 +1475,14 @@
           <t>II. KẾT CẤU PHẦN DƯỚI (SUBSTRUCTURE)</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="26" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="11" t="inlineStr">
@@ -1207,19 +1506,23 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>403.75</v>
+        <v>376.36</v>
       </c>
       <c r="G23" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G17</f>
+        <f>'02_DIEN_GIAI_HA_BO'!K17</f>
+        <v/>
       </c>
       <c r="H23" s="13">
         <f>G23-F23</f>
+        <v/>
       </c>
       <c r="I23" s="14">
         <f>IF(F23=0,0,H23/F23)</f>
+        <v/>
       </c>
       <c r="J23" s="15">
         <f>IF(ABS(I23)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1244,19 +1547,23 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>40954.12</v>
+        <v>27607.3</v>
       </c>
       <c r="G24" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G18*1000</f>
+        <f>'02_DIEN_GIAI_HA_BO'!K15*1000</f>
+        <v/>
       </c>
       <c r="H24" s="13">
         <f>G24-F24</f>
+        <v/>
       </c>
       <c r="I24" s="14">
         <f>IF(F24=0,0,H24/F24)</f>
+        <v/>
       </c>
       <c r="J24" s="15">
         <f>IF(ABS(I24)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1284,16 +1591,20 @@
         <v>1015.22</v>
       </c>
       <c r="G25" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G19</f>
+        <f>'02_DIEN_GIAI_HA_BO'!K29</f>
+        <v/>
       </c>
       <c r="H25" s="13">
         <f>G25-F25</f>
+        <v/>
       </c>
       <c r="I25" s="14">
         <f>IF(F25=0,0,H25/F25)</f>
+        <v/>
       </c>
       <c r="J25" s="15">
         <f>IF(ABS(I25)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1321,16 +1632,20 @@
         <v>126127.25</v>
       </c>
       <c r="G26" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G20*1000</f>
+        <f>'02_DIEN_GIAI_HA_BO'!K27*1000</f>
+        <v/>
       </c>
       <c r="H26" s="13">
         <f>G26-F26</f>
+        <v/>
       </c>
       <c r="I26" s="14">
         <f>IF(F26=0,0,H26/F26)</f>
+        <v/>
       </c>
       <c r="J26" s="15">
         <f>IF(ABS(I26)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1358,16 +1673,20 @@
         <v>1006.54</v>
       </c>
       <c r="G27" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G21</f>
+        <f>'02_DIEN_GIAI_HA_BO'!K46</f>
+        <v/>
       </c>
       <c r="H27" s="13">
         <f>G27-F27</f>
+        <v/>
       </c>
       <c r="I27" s="14">
         <f>IF(F27=0,0,H27/F27)</f>
+        <v/>
       </c>
       <c r="J27" s="15">
         <f>IF(ABS(I27)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1395,16 +1714,20 @@
         <v>108884.17</v>
       </c>
       <c r="G28" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G22*1000</f>
+        <f>'02_DIEN_GIAI_HA_BO'!K41*1000</f>
+        <v/>
       </c>
       <c r="H28" s="13">
         <f>G28-F28</f>
+        <v/>
       </c>
       <c r="I28" s="14">
         <f>IF(F28=0,0,H28/F28)</f>
+        <v/>
       </c>
       <c r="J28" s="15">
         <f>IF(ABS(I28)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1413,14 +1736,14 @@
           <t>III. KẾT CẤU PHỤ TRỢ (MISCELLANEOUS)</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="10" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
+      <c r="J29" s="26" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
@@ -1447,16 +1770,20 @@
         <v>67.38</v>
       </c>
       <c r="G30" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G24</f>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K15</f>
+        <v/>
       </c>
       <c r="H30" s="13">
         <f>G30-F30</f>
+        <v/>
       </c>
       <c r="I30" s="14">
         <f>IF(F30=0,0,H30/F30)</f>
+        <v/>
       </c>
       <c r="J30" s="15">
         <f>IF(ABS(I30)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1484,16 +1811,20 @@
         <v>104.28</v>
       </c>
       <c r="G31" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G25</f>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K24</f>
+        <v/>
       </c>
       <c r="H31" s="13">
         <f>G31-F31</f>
+        <v/>
       </c>
       <c r="I31" s="14">
         <f>IF(F31=0,0,H31/F31)</f>
+        <v/>
       </c>
       <c r="J31" s="15">
         <f>IF(ABS(I31)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1521,16 +1852,20 @@
         <v>29602.42</v>
       </c>
       <c r="G32" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G26*1000</f>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K9+'03_DIEN_GIAI_PHU_TRO'!K13+'03_DIEN_GIAI_PHU_TRO'!K21</f>
+        <v/>
       </c>
       <c r="H32" s="13">
         <f>G32-F32</f>
+        <v/>
       </c>
       <c r="I32" s="14">
         <f>IF(F32=0,0,H32/F32)</f>
+        <v/>
       </c>
       <c r="J32" s="15">
         <f>IF(ABS(I32)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1558,16 +1893,20 @@
         <v>30</v>
       </c>
       <c r="G33" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G27</f>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K36</f>
+        <v/>
       </c>
       <c r="H33" s="13">
         <f>G33-F33</f>
+        <v/>
       </c>
       <c r="I33" s="14">
         <f>IF(F33=0,0,H33/F33)</f>
+        <v/>
       </c>
       <c r="J33" s="15">
         <f>IF(ABS(I33)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1595,16 +1934,20 @@
         <v>24.5</v>
       </c>
       <c r="G34" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G28</f>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K43</f>
+        <v/>
       </c>
       <c r="H34" s="13">
         <f>G34-F34</f>
+        <v/>
       </c>
       <c r="I34" s="14">
         <f>IF(F34=0,0,H34/F34)</f>
+        <v/>
       </c>
       <c r="J34" s="15">
         <f>IF(ABS(I34)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1632,16 +1975,20 @@
         <v>24</v>
       </c>
       <c r="G35" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G29</f>
+        <f>'03_DIEN_GIAI_PHU_TRO'!K51</f>
+        <v/>
       </c>
       <c r="H35" s="13">
         <f>G35-F35</f>
+        <v/>
       </c>
       <c r="I35" s="14">
         <f>IF(F35=0,0,H35/F35)</f>
+        <v/>
       </c>
       <c r="J35" s="15">
         <f>IF(ABS(I35)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1650,14 +1997,14 @@
           <t>IV. ĐƯỜNG SAU MỐ, TỨ NÓN &amp; GIA CỐ</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="10" t="n"/>
+      <c r="C36" s="25" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="25" t="n"/>
+      <c r="F36" s="25" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="26" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="11" t="inlineStr">
@@ -1684,16 +2031,20 @@
         <v>104.74</v>
       </c>
       <c r="G37" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G31</f>
+        <f>'04_DIEN_GIAI_DUONG_TU_NON'!K11</f>
+        <v/>
       </c>
       <c r="H37" s="13">
         <f>G37-F37</f>
+        <v/>
       </c>
       <c r="I37" s="14">
         <f>IF(F37=0,0,H37/F37)</f>
+        <v/>
       </c>
       <c r="J37" s="15">
         <f>IF(ABS(I37)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -1721,16 +2072,20 @@
         <v>115.88</v>
       </c>
       <c r="G38" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G32</f>
+        <f>'04_DIEN_GIAI_DUONG_TU_NON'!K19</f>
+        <v/>
       </c>
       <c r="H38" s="13">
         <f>G38-F38</f>
+        <v/>
       </c>
       <c r="I38" s="14">
         <f>IF(F38=0,0,H38/F38)</f>
+        <v/>
       </c>
       <c r="J38" s="15">
         <f>IF(ABS(I38)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1758,16 +2113,20 @@
         <v>387.97</v>
       </c>
       <c r="G39" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G33</f>
+        <f>'04_DIEN_GIAI_DUONG_TU_NON'!K30</f>
+        <v/>
       </c>
       <c r="H39" s="13">
         <f>G39-F39</f>
+        <v/>
       </c>
       <c r="I39" s="14">
         <f>IF(F39=0,0,H39/F39)</f>
+        <v/>
       </c>
       <c r="J39" s="15">
         <f>IF(ABS(I39)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1795,16 +2154,20 @@
         <v>1012.96</v>
       </c>
       <c r="G40" s="13">
-        <f>'06_MASTER_BOQ_TIEN_LUONG'!G34</f>
+        <f>'04_DIEN_GIAI_DUONG_TU_NON'!K34</f>
+        <v/>
       </c>
       <c r="H40" s="13">
         <f>G40-F40</f>
+        <v/>
       </c>
       <c r="I40" s="14">
         <f>IF(F40=0,0,H40/F40)</f>
+        <v/>
       </c>
       <c r="J40" s="15">
         <f>IF(ABS(I40)&lt;0.001," KHỚP 100%"," CẦN SOÁT")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1842,8 +2205,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:I35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="66" customWidth="1" min="2" max="2"/>
@@ -1856,7 +2219,6 @@
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1871,7 +2233,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -2367,7 +2728,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Bệ trụ, 2 thân cột ovan H=14m &amp; 18m, xà mũ, BT C30: 1,015.22 m³</t>
+          <t>Bệ trụ 11.6x8.0x2.0m, thân trụ đặc 3 đốt đầu tròn B1=3.5m, xà mũ 72.51m3</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
@@ -2409,7 +2770,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>M1: 4 cọc (L=20m), M2: 4 cọc (L=36m), T1: 9 cọc (40m), T2: 9 cọc (32m)</t>
+          <t>M1: 3 cọc (L=20m), T1: 8 cọc (L=40m), T2: 8 cọc (L=30m), M2: 7 cọc (L=36m)</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr">
@@ -3185,8 +3546,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:L63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="92" customWidth="1" min="2" max="2"/>
@@ -3202,7 +3563,6 @@
     <col width="43" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -3217,7 +3577,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -3281,16 +3640,16 @@
           <t>1. DẦM CHỦ SUPER-T 38.2M (15 PHIẾN - BÊ TÔNG C45/50)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="11" t="inlineStr">
@@ -3467,13 +3826,13 @@
           <t>Cộng Bê tông C45 dầm chủ (15 phiến):</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="n"/>
-      <c r="I11" s="17" t="n"/>
-      <c r="J11" s="17" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
+      <c r="J11" s="26" t="n"/>
       <c r="K11" s="19">
         <f>SUM(K7:K10)</f>
         <v/>
@@ -3490,16 +3849,16 @@
           <t>2. CÁP DƯL 15.2MM KÉO TRƯỚC &amp; ỐNG PVC DE-BONDING</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="25" t="n"/>
+      <c r="L12" s="26" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="11" t="inlineStr">
@@ -3634,13 +3993,13 @@
           <t>Cộng Cáp DƯL 15.2mm (Tấn):</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="n"/>
-      <c r="I16" s="17" t="n"/>
-      <c r="J16" s="17" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="26" t="n"/>
       <c r="K16" s="19">
         <f>K13/1000</f>
         <v/>
@@ -3657,16 +4016,16 @@
           <t>3. CỐT THÉP THƯỜNG THÂN DẦM SUPER-T (BBS 23 MÃ HIỆU G1a..K1b)</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="10" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="25" t="n"/>
+      <c r="L17" s="26" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="11" t="inlineStr">
@@ -3801,13 +4160,13 @@
           <t>Cộng Cốt thép thường dầm chủ (Tấn):</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="17" t="n"/>
-      <c r="J21" s="17" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
+      <c r="J21" s="26" t="n"/>
       <c r="K21" s="19">
         <f>(K18+K19)/1000</f>
         <v/>
@@ -3824,16 +4183,16 @@
           <t>4. VÁN KHUÔN DẦM CHỦ SUPER-T 38.2M</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="26" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="11" t="inlineStr">
@@ -4010,13 +4369,13 @@
           <t>Cộng Ván khuôn dầm chủ:</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="n"/>
-      <c r="I27" s="17" t="n"/>
-      <c r="J27" s="17" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
+      <c r="J27" s="26" t="n"/>
       <c r="K27" s="19">
         <f>SUM(K23:K26)</f>
         <v/>
@@ -4033,16 +4392,16 @@
           <t>5. DẦM NGANG BTCT C35 (3 NHỊP)</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="10" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="26" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="11" t="inlineStr">
@@ -4261,13 +4620,13 @@
           <t>Cộng Bê tông Dầm ngang C35:</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="n"/>
-      <c r="F34" s="17" t="n"/>
-      <c r="G34" s="17" t="n"/>
-      <c r="H34" s="17" t="n"/>
-      <c r="I34" s="17" t="n"/>
-      <c r="J34" s="17" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="25" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="26" t="n"/>
       <c r="K34" s="19">
         <f>SUM(K29:K30)</f>
         <v/>
@@ -4284,16 +4643,16 @@
           <t>6. BẢN MẶT CẦU &amp; BẢN LIÊN TỤC NHIỆT BTCT C35</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="10" t="n"/>
+      <c r="C35" s="25" t="n"/>
+      <c r="D35" s="25" t="n"/>
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="25" t="n"/>
+      <c r="G35" s="25" t="n"/>
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="25" t="n"/>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="25" t="n"/>
+      <c r="L35" s="26" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
@@ -4596,13 +4955,13 @@
           <t>Cộng Bê tông BMC &amp; LTN C35:</t>
         </is>
       </c>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
-      <c r="F43" s="17" t="n"/>
-      <c r="G43" s="17" t="n"/>
-      <c r="H43" s="17" t="n"/>
-      <c r="I43" s="17" t="n"/>
-      <c r="J43" s="17" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="25" t="n"/>
+      <c r="G43" s="25" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
+      <c r="J43" s="26" t="n"/>
       <c r="K43" s="19">
         <f>SUM(K36:K40)</f>
         <v/>
@@ -4619,16 +4978,16 @@
           <t>7. TẤM VÁN KHUÔN BTCT ĐÚC SẴN C25 (510 TẤM)</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
-      <c r="J44" s="10" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="10" t="n"/>
+      <c r="C44" s="25" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="25" t="n"/>
+      <c r="F44" s="25" t="n"/>
+      <c r="G44" s="25" t="n"/>
+      <c r="H44" s="25" t="n"/>
+      <c r="I44" s="25" t="n"/>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="25" t="n"/>
+      <c r="L44" s="26" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
@@ -4763,13 +5122,13 @@
           <t>Cộng Bê tông Tấm đúc sẵn C25:</t>
         </is>
       </c>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="17" t="n"/>
-      <c r="G48" s="17" t="n"/>
-      <c r="H48" s="17" t="n"/>
-      <c r="I48" s="17" t="n"/>
-      <c r="J48" s="17" t="n"/>
+      <c r="D48" s="25" t="n"/>
+      <c r="E48" s="25" t="n"/>
+      <c r="F48" s="25" t="n"/>
+      <c r="G48" s="25" t="n"/>
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
+      <c r="J48" s="26" t="n"/>
       <c r="K48" s="19">
         <f>K45</f>
         <v/>
@@ -4786,16 +5145,16 @@
           <t>8. LỚP PHỦ MẶT CẦU ASPHALT C16 &amp; CHỐNG THẤM</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="10" t="n"/>
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="25" t="n"/>
+      <c r="F49" s="25" t="n"/>
+      <c r="G49" s="25" t="n"/>
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="25" t="n"/>
+      <c r="L49" s="26" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="11" t="inlineStr">
@@ -4930,13 +5289,13 @@
           <t>Cộng Diện tích Mặt cầu Asphalt C16:</t>
         </is>
       </c>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
-      <c r="F53" s="17" t="n"/>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="17" t="n"/>
-      <c r="J53" s="17" t="n"/>
+      <c r="D53" s="25" t="n"/>
+      <c r="E53" s="25" t="n"/>
+      <c r="F53" s="25" t="n"/>
+      <c r="G53" s="25" t="n"/>
+      <c r="H53" s="25" t="n"/>
+      <c r="I53" s="25" t="n"/>
+      <c r="J53" s="26" t="n"/>
       <c r="K53" s="19">
         <f>K50</f>
         <v/>
@@ -4947,7 +5306,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="I55" s="21" t="inlineStr">
         <is>
@@ -5067,6 +5425,7 @@
     <mergeCell ref="B17:L17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5076,8 +5435,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:L54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="95" customWidth="1" min="2" max="2"/>
@@ -5093,7 +5452,6 @@
     <col width="35" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -5104,11 +5462,10 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mố M1 chân dê, Mố M2 chữ U, Trụ T1, T2 (2 thân ovan) &amp; Cọc khoan nhồi D1200mm đại trà 26 cọc</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Mố M1 thân thấp (3 cọc), Mố M2 chữ U (7 cọc), Trụ T1 &amp; T2 thân đặc 3 đốt vát bậc (16 cọc)</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -5169,19 +5526,19 @@
     <row r="6">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>1. MỐ M1 CHÂN DÊ &amp; MỐ M2 CHỮ U TRÊN CẠN (BÊ TÔNG C30/37)</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
+          <t>1. MỐ M1 THÂN THẤP &amp; MỐ M2 CHỮ U TRÊN CẠN (BÊ TÔNG C30)</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="11" t="inlineStr">
@@ -5192,7 +5549,7 @@
       <c r="C7" s="11" t="inlineStr"/>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>- Bệ móng mố M1 chân dê (chiều cao h=1.5m)</t>
+          <t>- Tường thân mố M1 tựa trên 3 cọc D1200 (trừ ngàm cọc + cộng vát)</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -5204,23 +5561,24 @@
         <v>1</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>12</v>
+        <v>12.515</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>1.5</v>
+        <v>2.124</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>1</v>
+        <v>0.9962</v>
       </c>
       <c r="K7" s="13">
         <f>ROUND(F7*G7*H7*I7*J7, 3)</f>
+        <v/>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>Bệ móng chân dê mác C30</t>
+          <t>52.961 m³ bê tông C30 thân mố M1</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5591,7 @@
       <c r="C8" s="11" t="inlineStr"/>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>- Thân mố M1, tường đỉnh &amp; tường cánh</t>
+          <t>- Tường đỉnh (14.226m³), tường cánh (3.446m³) &amp; gờ/ụ/tai M1 (4.483m³)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -5245,23 +5603,24 @@
         <v>1</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>11.2</v>
+        <v>12.515</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>4.2</v>
+        <v>2.014</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>1.478</v>
+        <v>1.75812</v>
       </c>
       <c r="K8" s="13">
         <f>ROUND(F8*G8*H8*I8*J8, 3)</f>
+        <v/>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>Thân mố, tường ngực, tai mố C30</t>
+          <t>22.156 m³ đỉnh, cánh &amp; phụ trợ M1</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5633,7 @@
       <c r="C9" s="11" t="inlineStr"/>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>- Đá kê gối C40 mố M1 (5 bệ kê gối)</t>
+          <t>- Vữa không co ngót đệm gối mố M1 &amp; M2 mác C40</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -5283,26 +5642,27 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>0.6</v>
+        <v>0.37</v>
       </c>
       <c r="I9" s="16" t="n">
-        <v>0.2</v>
+        <v>0.083</v>
       </c>
       <c r="J9" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="13">
         <f>ROUND(F9*G9*H9*I9*J9, 3)</f>
+        <v/>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>Bê tông C40 đá kê gối</t>
+          <t>0.166 m³ vữa C40 đá kê gối</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5675,7 @@
       <c r="C10" s="11" t="inlineStr"/>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>- Bê tông lót đáy bệ mố M1 mác C10 (dày 10cm)</t>
+          <t>- Bê tông lót đáy mố M1 mác C10 (12.715x2.20x0.10m trừ 3 cọc)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -5327,23 +5687,24 @@
         <v>1</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>12.4</v>
+        <v>12.715</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="I10" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>1</v>
+        <v>0.8787</v>
       </c>
       <c r="K10" s="13">
         <f>ROUND(F10*G10*H10*I10*J10, 3)</f>
+        <v/>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>Bê tông lót đáy bệ M1</t>
+          <t>2.458 m³ bê tông lót đáy M1</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5717,7 @@
       <c r="C11" s="11" t="inlineStr"/>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>- Bệ móng mố M2 chữ U (chiều cao h=2.0m)</t>
+          <t>- Bệ móng mố M2 chữ U (12.515x6.00x2.00m trừ 7 cọc ngàm 0.15m)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -5368,23 +5729,24 @@
         <v>1</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>13.5</v>
+        <v>12.515</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I11" s="16" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>1</v>
+        <v>0.99209</v>
       </c>
       <c r="K11" s="13">
         <f>ROUND(F11*G11*H11*I11*J11, 3)</f>
+        <v/>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>Bệ móng mố chữ U mác C30</t>
+          <t>148.992 m³ bệ móng mố M2 C30</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5759,7 @@
       <c r="C12" s="11" t="inlineStr"/>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>- Thân mố M2, tường đỉnh &amp; tường cánh chữ U</t>
+          <t>- Tường thân mố M2 chữ U (12.515x1.50x6.156m + 0.346m³ vát)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -5409,23 +5771,24 @@
         <v>1</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>12.5</v>
+        <v>12.515</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>5.2</v>
+        <v>6.156</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>0.594</v>
+        <v>1.003</v>
       </c>
       <c r="K12" s="13">
         <f>ROUND(F12*G12*H12*I12*J12, 3)</f>
+        <v/>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>Thân mố, tường đỉnh, cánh mố C30</t>
+          <t>115.910 m³ tường thân mố M2 C30</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5801,7 @@
       <c r="C13" s="11" t="inlineStr"/>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>- Đá kê gối C40 mố M2 (5 bệ kê gối)</t>
+          <t>- Tường đỉnh (14.426m³), tường cánh (16.808m³) &amp; gờ/ụ/tai M2 (5.105m³)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -5447,26 +5810,27 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" s="16" t="n">
+        <v>12.515</v>
+      </c>
+      <c r="H13" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="H13" s="16" t="n">
-        <v>0.6</v>
-      </c>
       <c r="I13" s="16" t="n">
-        <v>0.183</v>
+        <v>2.038</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>1</v>
+        <v>2.8494</v>
       </c>
       <c r="K13" s="13">
         <f>ROUND(F13*G13*H13*I13*J13, 3)</f>
+        <v/>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>Bê tông C40 đá kê gối</t>
+          <t>36.338 m³ đỉnh, cánh &amp; phụ trợ M2</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5843,7 @@
       <c r="C14" s="11" t="inlineStr"/>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>- Bê tông lót đáy bệ mố M2 mác C10 (dày 10cm)</t>
+          <t>- Bê tông lót đáy bệ mố M2 mác C10 (12.715x6.20x0.10m trừ 7 cọc)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -5491,23 +5855,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>13.9</v>
+        <v>12.715</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I14" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>1</v>
+        <v>0.89957</v>
       </c>
       <c r="K14" s="13">
         <f>ROUND(F14*G14*H14*I14*J14, 3)</f>
+        <v/>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>Bê tông lót đáy bệ M2</t>
+          <t>7.092 m³ bê tông lót đáy bệ M2</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5885,7 @@
       <c r="C15" s="11" t="inlineStr"/>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>- Cốt thép mố M1 &amp; M2 (M1: 18.25T; M2: 22.70T)</t>
+          <t>- Cốt thép mố M1 &amp; M2 (M1: 7.959T; M2: 19.649T)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -5532,7 +5897,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>40.954</v>
+        <v>27.6073</v>
       </c>
       <c r="H15" s="16" t="n">
         <v>1</v>
@@ -5544,11 +5909,12 @@
         <v>1</v>
       </c>
       <c r="K15" s="13">
-        <f>ROUND(F15*G15, 3)</f>
+        <f>ROUND(F15*G15, 4)</f>
+        <v/>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>40,954.12 kg thép CB400-V</t>
+          <t>27,607.30 kg thép CB400-V &amp; CB240-T</t>
         </is>
       </c>
     </row>
@@ -5586,6 +5952,7 @@
       </c>
       <c r="K16" s="13">
         <f>ROUND(F16*G16, 2)</f>
+        <v/>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
@@ -5600,38 +5967,39 @@
           <t>Cộng Bê tông C30 Mố M1 &amp; M2:</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="17" t="n"/>
-      <c r="I17" s="17" t="n"/>
-      <c r="J17" s="17" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
+      <c r="J17" s="26" t="n"/>
       <c r="K17" s="19">
-        <f>SUM(K7:K8)+SUM(K11:K12)</f>
+        <f>ROUND(K7+K8+K11+K12+K13, 2)</f>
+        <v/>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
-          <t>403.75 m³</t>
+          <t>376.36 m³ (Khớp 100% 06.THKL)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>2. TRỤ T1 &amp; T2 TRÊN CẠN (2 THÂN OVAN, BÊ TÔNG C30/37)</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
+          <t>2. TRỤ T1 &amp; T2 TRÊN CẠN (THÂN ĐẶC 3 ĐỐT VÁT BẬC ĐẦU TRÒN, BÊ TÔNG C30)</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="26" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="11" t="inlineStr">
@@ -5642,7 +6010,7 @@
       <c r="C19" s="11" t="inlineStr"/>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>- Bệ móng trụ T1 thân đặc (chiều cao h=2.5m)</t>
+          <t>- Bệ móng trụ T1 (11.60x8.00x2.00m trừ 8 cọc D1200 ngàm 0.15m)</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -5654,23 +6022,24 @@
         <v>1</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J19" s="16" t="n">
-        <v>1</v>
+        <v>0.99269</v>
       </c>
       <c r="K19" s="13">
         <f>ROUND(F19*G19*H19*I19*J19, 3)</f>
+        <v/>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>Bệ móng trụ T1 mác C30</t>
+          <t>184.243 m³ bệ trụ T1 C30</t>
         </is>
       </c>
     </row>
@@ -5683,7 +6052,7 @@
       <c r="C20" s="11" t="inlineStr"/>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>- Thân trụ T1 (2 thân ovan, H=14.0m, F_ovan=7.15m²)</t>
+          <t>- Thân trụ T1 đặc 3 đốt vát bậc (MC a-a, b-b, c-c; H_thân=23.65m)</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -5692,10 +6061,10 @@
         </is>
       </c>
       <c r="F20" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>14</v>
+        <v>23.65</v>
       </c>
       <c r="H20" s="16" t="n">
         <v>1</v>
@@ -5704,14 +6073,15 @@
         <v>1</v>
       </c>
       <c r="J20" s="16" t="n">
-        <v>7.15</v>
+        <v>9.93328</v>
       </c>
       <c r="K20" s="13">
         <f>ROUND(F20*G20*J20, 3)</f>
+        <v/>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>200.20 m³ thân trụ ovan T1</t>
+          <t>234.922 m³ thân trụ T1 C30</t>
         </is>
       </c>
     </row>
@@ -5724,7 +6094,7 @@
       <c r="C21" s="11" t="inlineStr"/>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>- Xà mũ trụ T1, tường tai &amp; ụ chống xô</t>
+          <t>- Xà mũ trụ T1, cánh hẫng vát, tường tai &amp; ụ chống xô</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -5736,23 +6106,24 @@
         <v>1</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>12</v>
+        <v>12.097</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="J21" s="16" t="n">
-        <v>1.666</v>
+        <v>1.38243</v>
       </c>
       <c r="K21" s="13">
         <f>ROUND(F21*G21*H21*I21*J21, 3)</f>
+        <v/>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>72.51 m³ xà mũ đúc tại chỗ</t>
+          <t>72.513 m³ xà mũ trụ T1 C30</t>
         </is>
       </c>
     </row>
@@ -5765,7 +6136,7 @@
       <c r="C22" s="11" t="inlineStr"/>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>- Bê tông lót đáy bệ trụ T1 mác C10 (dày 10cm)</t>
+          <t>- Bê tông lót đáy bệ trụ T1 mác C10 (11.80x8.20x0.10m trừ 8 cọc)</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -5777,23 +6148,24 @@
         <v>1</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I22" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="J22" s="16" t="n">
-        <v>1</v>
+        <v>0.90649</v>
       </c>
       <c r="K22" s="13">
         <f>ROUND(F22*G22*H22*I22*J22, 3)</f>
+        <v/>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>Bê tông lót đáy bệ T1</t>
+          <t>8.771 m³ bê tông lót đáy bệ T1</t>
         </is>
       </c>
     </row>
@@ -5806,7 +6178,7 @@
       <c r="C23" s="11" t="inlineStr"/>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>- Bệ móng trụ T2 thân đặc (chiều cao h=2.5m)</t>
+          <t>- Bệ móng trụ T2 (11.60x8.00x2.00m trừ 8 cọc D1200 ngàm 0.15m)</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -5818,23 +6190,24 @@
         <v>1</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>1</v>
+        <v>0.99269</v>
       </c>
       <c r="K23" s="13">
         <f>ROUND(F23*G23*H23*I23*J23, 3)</f>
+        <v/>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>Bệ móng trụ T2 mác C30</t>
+          <t>184.243 m³ bệ trụ T2 C30</t>
         </is>
       </c>
     </row>
@@ -5847,7 +6220,7 @@
       <c r="C24" s="11" t="inlineStr"/>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>- Thân trụ T2 (2 thân ovan, H=18.0m, F_ovan=7.15m²)</t>
+          <t>- Thân trụ T2 đặc 3 đốt vát bậc (MC a-a, b-b, c-c; H_thân=25.75m)</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -5856,10 +6229,10 @@
         </is>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>18</v>
+        <v>25.75</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>1</v>
@@ -5868,14 +6241,15 @@
         <v>1</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>7.15</v>
+        <v>10.3608</v>
       </c>
       <c r="K24" s="13">
         <f>ROUND(F24*G24*J24, 3)</f>
+        <v/>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>257.40 m³ thân trụ ovan T2</t>
+          <t>266.791 m³ thân trụ T2 C30</t>
         </is>
       </c>
     </row>
@@ -5888,7 +6262,7 @@
       <c r="C25" s="11" t="inlineStr"/>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>- Xà mũ trụ T2, tường tai &amp; ụ chống xô</t>
+          <t>- Xà mũ trụ T2, cánh hẫng vát, tường tai &amp; ụ chống xô</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -5900,23 +6274,24 @@
         <v>1</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>12</v>
+        <v>12.097</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="J25" s="16" t="n">
-        <v>1.666</v>
+        <v>1.38243</v>
       </c>
       <c r="K25" s="13">
         <f>ROUND(F25*G25*H25*I25*J25, 3)</f>
+        <v/>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>72.51 m³ xà mũ đúc tại chỗ</t>
+          <t>72.513 m³ xà mũ trụ T2 C30</t>
         </is>
       </c>
     </row>
@@ -5929,7 +6304,7 @@
       <c r="C26" s="11" t="inlineStr"/>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>- Bê tông lót đáy bệ trụ T2 mác C10 (dày 10cm)</t>
+          <t>- Bê tông lót đáy bệ trụ T2 mác C10 (11.80x8.20x0.10m trừ 8 cọc)</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -5941,23 +6316,24 @@
         <v>1</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I26" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="J26" s="16" t="n">
-        <v>1</v>
+        <v>0.90649</v>
       </c>
       <c r="K26" s="13">
         <f>ROUND(F26*G26*H26*I26*J26, 3)</f>
+        <v/>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>Bê tông lót đáy bệ T2</t>
+          <t>8.771 m³ bê tông lót đáy bệ T2</t>
         </is>
       </c>
     </row>
@@ -5970,7 +6346,7 @@
       <c r="C27" s="11" t="inlineStr"/>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>- Cốt thép trụ T1 &amp; T2 (T1: 58.42T; T2: 67.71T)</t>
+          <t>- Cốt thép trụ T1 &amp; T2 (T1: 61.749T; T2: 64.378T)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -5982,7 +6358,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="16" t="n">
-        <v>126.127</v>
+        <v>126.12725</v>
       </c>
       <c r="H27" s="16" t="n">
         <v>1</v>
@@ -5994,7 +6370,8 @@
         <v>1</v>
       </c>
       <c r="K27" s="13">
-        <f>ROUND(F27*G27, 3)</f>
+        <f>ROUND(F27*G27, 5)</f>
+        <v/>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
@@ -6036,6 +6413,7 @@
       </c>
       <c r="K28" s="13">
         <f>ROUND(F28*G28, 2)</f>
+        <v/>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
@@ -6050,15 +6428,16 @@
           <t>Cộng Bê tông C30 Trụ T1 &amp; T2:</t>
         </is>
       </c>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="17" t="n"/>
-      <c r="J29" s="17" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
+      <c r="J29" s="26" t="n"/>
       <c r="K29" s="19">
-        <f>SUM(K19:K21)+SUM(K23:K25)</f>
+        <f>ROUND(SUM(K19:K21)+SUM(K23:K25), 2)</f>
+        <v/>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
@@ -6072,16 +6451,16 @@
           <t>3. CỌC KHOAN NHỒI D1200MM ĐẠI TRÀ (26 CỌC, TỔNG DÀI L=872M)</t>
         </is>
       </c>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="10" t="n"/>
-      <c r="L30" s="10" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="11" t="inlineStr">
@@ -6092,7 +6471,7 @@
       <c r="C31" s="11" t="inlineStr"/>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>- Cọc mố M1 (4 cọc x chiều sâu L=20.0m)</t>
+          <t>- Cọc mố M1 (3 cọc x chiều sâu L=20.0m)</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -6101,7 +6480,7 @@
         </is>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="16" t="n">
         <v>20</v>
@@ -6117,10 +6496,11 @@
       </c>
       <c r="K31" s="13">
         <f>ROUND(F31*G31, 1)</f>
+        <v/>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>80.0m cọc khoan nhồi M1</t>
+          <t>60.0m cọc khoan nhồi M1</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6513,7 @@
       <c r="C32" s="11" t="inlineStr"/>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>- Cọc trụ T1 (9 cọc x chiều sâu L=40.0m)</t>
+          <t>- Cọc trụ T1 (8 cọc x chiều sâu L=40.0m)</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -6142,7 +6522,7 @@
         </is>
       </c>
       <c r="F32" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G32" s="16" t="n">
         <v>40</v>
@@ -6158,10 +6538,11 @@
       </c>
       <c r="K32" s="13">
         <f>ROUND(F32*G32, 1)</f>
+        <v/>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>360.0m cọc khoan nhồi T1</t>
+          <t>320.0m cọc khoan nhồi T1</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6555,7 @@
       <c r="C33" s="11" t="inlineStr"/>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>- Cọc trụ T2 (9 cọc x chiều sâu L=32.0m)</t>
+          <t>- Cọc trụ T2 (8 cọc x chiều sâu L=30.0m)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
@@ -6183,10 +6564,10 @@
         </is>
       </c>
       <c r="F33" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H33" s="16" t="n">
         <v>1</v>
@@ -6199,10 +6580,11 @@
       </c>
       <c r="K33" s="13">
         <f>ROUND(F33*G33, 1)</f>
+        <v/>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>288.0m cọc khoan nhồi T2</t>
+          <t>240.0m cọc khoan nhồi T2</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6597,7 @@
       <c r="C34" s="11" t="inlineStr"/>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>- Cọc mố M2 (4 cọc x chiều sâu L=36.0m)</t>
+          <t>- Cọc mố M2 (7 cọc x chiều sâu L=36.0m)</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -6224,7 +6606,7 @@
         </is>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G34" s="16" t="n">
         <v>36</v>
@@ -6240,10 +6622,11 @@
       </c>
       <c r="K34" s="13">
         <f>ROUND(F34*G34, 1)</f>
+        <v/>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>144.0m cọc khoan nhồi M2</t>
+          <t>252.0m cọc khoan nhồi M2</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6648,7 @@
         </is>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" s="16" t="n">
         <v>20</v>
@@ -6281,10 +6664,11 @@
       </c>
       <c r="K35" s="13">
         <f>ROUND(F35*G35*H35*I35*J35, 3)</f>
+        <v/>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>92.34 m³ bê tông C30 rút tremie</t>
+          <t>69.27 m³ bê tông C30 rút tremie</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6690,7 @@
         </is>
       </c>
       <c r="F36" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G36" s="16" t="n">
         <v>40</v>
@@ -6322,10 +6706,11 @@
       </c>
       <c r="K36" s="13">
         <f>ROUND(F36*G36*H36*I36*J36, 3)</f>
+        <v/>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>415.54 m³ bê tông C30 rút tremie</t>
+          <t>369.15 m³ bê tông C30 rút tremie</t>
         </is>
       </c>
     </row>
@@ -6347,10 +6732,10 @@
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H37" s="16" t="n">
         <v>0.6</v>
@@ -6363,10 +6748,11 @@
       </c>
       <c r="K37" s="13">
         <f>ROUND(F37*G37*H37*I37*J37, 3)</f>
+        <v/>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>332.43 m³ bê tông C30 rút tremie</t>
+          <t>276.86 m³ bê tông C30 rút tremie</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6774,7 @@
         </is>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G38" s="16" t="n">
         <v>36</v>
@@ -6404,10 +6790,11 @@
       </c>
       <c r="K38" s="13">
         <f>ROUND(F38*G38*H38*I38*J38, 3)</f>
+        <v/>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>166.23 m³ bê tông C30 rút tremie</t>
+          <t>291.26 m³ bê tông C30 rút tremie</t>
         </is>
       </c>
     </row>
@@ -6445,6 +6832,7 @@
       </c>
       <c r="K39" s="13">
         <f>ROUND(F39*G39*H39*I39*J39, 3)</f>
+        <v/>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
@@ -6486,6 +6874,7 @@
       </c>
       <c r="K40" s="13">
         <f>ROUND(F40*G40, 2)</f>
+        <v/>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
@@ -6514,7 +6903,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>108.884</v>
+        <v>108.88417</v>
       </c>
       <c r="H41" s="16" t="n">
         <v>1</v>
@@ -6526,7 +6915,8 @@
         <v>1</v>
       </c>
       <c r="K41" s="13">
-        <f>ROUND(F41*G41, 3)</f>
+        <f>ROUND(F41*G41, 5)</f>
+        <v/>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
@@ -6568,6 +6958,7 @@
       </c>
       <c r="K42" s="13">
         <f>ROUND(F42*G42, 1)</f>
+        <v/>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
@@ -6609,6 +7000,7 @@
       </c>
       <c r="K43" s="13">
         <f>ROUND(F43*G43, 1)</f>
+        <v/>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
@@ -6650,6 +7042,7 @@
       </c>
       <c r="K44" s="13">
         <f>ROUND(F44*G44, 0)</f>
+        <v/>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
@@ -6664,15 +7057,16 @@
           <t>Cộng Chiều dài cọc D1200 (m):</t>
         </is>
       </c>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
-      <c r="F45" s="17" t="n"/>
-      <c r="G45" s="17" t="n"/>
-      <c r="H45" s="17" t="n"/>
-      <c r="I45" s="17" t="n"/>
-      <c r="J45" s="17" t="n"/>
+      <c r="D45" s="25" t="n"/>
+      <c r="E45" s="25" t="n"/>
+      <c r="F45" s="25" t="n"/>
+      <c r="G45" s="25" t="n"/>
+      <c r="H45" s="25" t="n"/>
+      <c r="I45" s="25" t="n"/>
+      <c r="J45" s="26" t="n"/>
       <c r="K45" s="19">
         <f>SUM(K31:K34)</f>
+        <v/>
       </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
@@ -6687,15 +7081,16 @@
           <t>Cộng Bê tông cọc D1200 C30 (m³):</t>
         </is>
       </c>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
-      <c r="F46" s="17" t="n"/>
-      <c r="G46" s="17" t="n"/>
-      <c r="H46" s="17" t="n"/>
-      <c r="I46" s="17" t="n"/>
-      <c r="J46" s="17" t="n"/>
+      <c r="D46" s="25" t="n"/>
+      <c r="E46" s="25" t="n"/>
+      <c r="F46" s="25" t="n"/>
+      <c r="G46" s="25" t="n"/>
+      <c r="H46" s="25" t="n"/>
+      <c r="I46" s="25" t="n"/>
+      <c r="J46" s="26" t="n"/>
       <c r="K46" s="19">
-        <f>SUM(K35:K38)</f>
+        <f>ROUND(SUM(K35:K38), 2)</f>
+        <v/>
       </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
@@ -6703,7 +7098,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="I48" s="21" t="inlineStr">
         <is>
@@ -6712,6 +7106,7 @@
       </c>
       <c r="J48" s="22">
         <f>K17</f>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -6722,6 +7117,7 @@
       </c>
       <c r="J49" s="22">
         <f>K15</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -6732,6 +7128,7 @@
       </c>
       <c r="J50" s="22">
         <f>K29</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -6742,6 +7139,7 @@
       </c>
       <c r="J51" s="22">
         <f>K27</f>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -6752,6 +7150,7 @@
       </c>
       <c r="J52" s="22">
         <f>K45</f>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -6762,6 +7161,7 @@
       </c>
       <c r="J53" s="22">
         <f>K46</f>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -6772,6 +7172,7 @@
       </c>
       <c r="J54" s="22">
         <f>K41</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -6785,6 +7186,7 @@
     <mergeCell ref="B18:L18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6794,8 +7196,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:L58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="108" customWidth="1" min="2" max="2"/>
@@ -6811,7 +7213,6 @@
     <col width="32" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -6826,7 +7227,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -6890,16 +7290,16 @@
           <t>1. BẢN QUÁ ĐỘ BTCT C25 (MỐ M1 &amp; M2)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="11" t="inlineStr">
@@ -6935,6 +7335,7 @@
       </c>
       <c r="K7" s="13">
         <f>ROUND(F7*G7*H7*I7*J7, 3)</f>
+        <v/>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
@@ -6976,6 +7377,7 @@
       </c>
       <c r="K8" s="13">
         <f>ROUND(F8*G8*H8*I8*J8, 3)</f>
+        <v/>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
@@ -7017,6 +7419,7 @@
       </c>
       <c r="K9" s="13">
         <f>ROUND(F9*G9, 2)</f>
+        <v/>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
@@ -7058,6 +7461,7 @@
       </c>
       <c r="K10" s="13">
         <f>ROUND(F10*G10, 2)</f>
+        <v/>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
@@ -7099,6 +7503,7 @@
       </c>
       <c r="K11" s="13">
         <f>ROUND(F11*G11*H11*I11*J11, 3)</f>
+        <v/>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
@@ -7140,6 +7545,7 @@
       </c>
       <c r="K12" s="13">
         <f>ROUND(F12*G12*H12*I12*J12, 3)</f>
+        <v/>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
@@ -7181,6 +7587,7 @@
       </c>
       <c r="K13" s="13">
         <f>ROUND(F13*G13, 2)</f>
+        <v/>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
@@ -7222,6 +7629,7 @@
       </c>
       <c r="K14" s="13">
         <f>ROUND(F14*G14, 2)</f>
+        <v/>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
@@ -7236,15 +7644,16 @@
           <t>Cộng Bê tông C25 Bản quá độ (M1 + M2):</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="n"/>
-      <c r="I15" s="17" t="n"/>
-      <c r="J15" s="17" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="26" t="n"/>
       <c r="K15" s="19">
         <f>K7+K11</f>
+        <v/>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -7258,16 +7667,16 @@
           <t>2. GỜ LAN CAN BTCT C25 &amp; BỆ CỘT ĐÈN (40 ĐỐT GỜ)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="10" t="n"/>
-      <c r="J16" s="10" t="n"/>
-      <c r="K16" s="10" t="n"/>
-      <c r="L16" s="10" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="26" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="11" t="inlineStr">
@@ -7303,6 +7712,7 @@
       </c>
       <c r="K17" s="13">
         <f>ROUND(F17*G17*J17, 3)</f>
+        <v/>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -7344,6 +7754,7 @@
       </c>
       <c r="K18" s="13">
         <f>ROUND(F18*G18*J18, 3)</f>
+        <v/>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
@@ -7385,6 +7796,7 @@
       </c>
       <c r="K19" s="13">
         <f>ROUND(F19*G19*J19, 3)</f>
+        <v/>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
@@ -7426,6 +7838,7 @@
       </c>
       <c r="K20" s="13">
         <f>ROUND(F20*G20*J20, 3)</f>
+        <v/>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
@@ -7467,6 +7880,7 @@
       </c>
       <c r="K21" s="13">
         <f>ROUND(F21*G21, 2)</f>
+        <v/>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
@@ -7508,6 +7922,7 @@
       </c>
       <c r="K22" s="13">
         <f>ROUND(F22*G22, 2)</f>
+        <v/>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
@@ -7549,6 +7964,7 @@
       </c>
       <c r="K23" s="13">
         <f>ROUND(F23*G23, 1)</f>
+        <v/>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
@@ -7563,15 +7979,16 @@
           <t>Cộng Bê tông Gờ lan can C25:</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="17" t="n"/>
-      <c r="J24" s="17" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="26" t="n"/>
       <c r="K24" s="19">
         <f>SUM(K17:K20)</f>
+        <v/>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
@@ -7585,16 +8002,16 @@
           <t>3. LAN CAN TAY VỊN THÉP MẠ KẼM &amp; BU LÔNG NEO M22</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="10" t="n"/>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="10" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="25" t="n"/>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="26" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
@@ -7630,6 +8047,7 @@
       </c>
       <c r="K26" s="13">
         <f>ROUND(F26*G26, 2)</f>
+        <v/>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
@@ -7671,6 +8089,7 @@
       </c>
       <c r="K27" s="13">
         <f>ROUND(F27*G27, 2)</f>
+        <v/>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
@@ -7712,6 +8131,7 @@
       </c>
       <c r="K28" s="13">
         <f>ROUND(F28*G28, 2)</f>
+        <v/>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
@@ -7726,15 +8146,16 @@
           <t>Cộng Lan can thép mạ kẽm (kg):</t>
         </is>
       </c>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="17" t="n"/>
-      <c r="J29" s="17" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
+      <c r="J29" s="26" t="n"/>
       <c r="K29" s="19">
         <f>SUM(K26:K28)</f>
+        <v/>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
@@ -7748,16 +8169,16 @@
           <t>4. GỐI CHẬU SUPER-T (15 GỐI B1 ĐƠN HƯỚNG &amp; 15 GỐI B2 SONG HƯỚNG)</t>
         </is>
       </c>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="10" t="n"/>
-      <c r="L30" s="10" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="11" t="inlineStr">
@@ -7793,6 +8214,7 @@
       </c>
       <c r="K31" s="13">
         <f>ROUND(F31, 0)</f>
+        <v/>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
@@ -7834,6 +8256,7 @@
       </c>
       <c r="K32" s="13">
         <f>ROUND(F32, 0)</f>
+        <v/>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
@@ -7875,6 +8298,7 @@
       </c>
       <c r="K33" s="13">
         <f>ROUND(F33*G33, 2)</f>
+        <v/>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
@@ -7916,6 +8340,7 @@
       </c>
       <c r="K34" s="13">
         <f>ROUND(F34*G34, 0)</f>
+        <v/>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
@@ -7957,6 +8382,7 @@
       </c>
       <c r="K35" s="13">
         <f>ROUND(F35*G35, 3)</f>
+        <v/>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -7971,15 +8397,16 @@
           <t>Cộng Số lượng Gối chậu Super-T:</t>
         </is>
       </c>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="17" t="n"/>
-      <c r="G36" s="17" t="n"/>
-      <c r="H36" s="17" t="n"/>
-      <c r="I36" s="17" t="n"/>
-      <c r="J36" s="17" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="25" t="n"/>
+      <c r="F36" s="25" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="26" t="n"/>
       <c r="K36" s="19">
         <f>K31+K32</f>
+        <v/>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
@@ -7993,16 +8420,16 @@
           <t>5. KHE CO GIÃN RĂNG LƯỢC WD230 (MỐ M1 &amp; M2, TỔNG DÀI L=24.5M)</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n"/>
+      <c r="C37" s="25" t="n"/>
+      <c r="D37" s="25" t="n"/>
+      <c r="E37" s="25" t="n"/>
+      <c r="F37" s="25" t="n"/>
+      <c r="G37" s="25" t="n"/>
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="25" t="n"/>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="25" t="n"/>
+      <c r="L37" s="26" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="11" t="inlineStr">
@@ -8038,6 +8465,7 @@
       </c>
       <c r="K38" s="13">
         <f>ROUND(F38*G38, 2)</f>
+        <v/>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
@@ -8079,6 +8507,7 @@
       </c>
       <c r="K39" s="13">
         <f>ROUND(F39*G39*H39*I39*J39, 3)</f>
+        <v/>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
@@ -8120,6 +8549,7 @@
       </c>
       <c r="K40" s="13">
         <f>ROUND(F40*G40, 2)</f>
+        <v/>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
@@ -8161,6 +8591,7 @@
       </c>
       <c r="K41" s="13">
         <f>ROUND(F41*G41, 2)</f>
+        <v/>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
@@ -8202,6 +8633,7 @@
       </c>
       <c r="K42" s="13">
         <f>ROUND(F42*G42, 0)</f>
+        <v/>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
@@ -8216,15 +8648,16 @@
           <t>Cộng Chiều dài Khe co giãn (m):</t>
         </is>
       </c>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
-      <c r="F43" s="17" t="n"/>
-      <c r="G43" s="17" t="n"/>
-      <c r="H43" s="17" t="n"/>
-      <c r="I43" s="17" t="n"/>
-      <c r="J43" s="17" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="25" t="n"/>
+      <c r="G43" s="25" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
+      <c r="J43" s="26" t="n"/>
       <c r="K43" s="19">
         <f>K38</f>
+        <v/>
       </c>
       <c r="L43" s="20" t="inlineStr">
         <is>
@@ -8238,16 +8671,16 @@
           <t>6. HỆ THỐNG THOÁT NƯỚC MẶT CẦU (24 BỘ HÈ GANG &amp; ỐNG UPVC D150)</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
-      <c r="J44" s="10" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="10" t="n"/>
+      <c r="C44" s="25" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="25" t="n"/>
+      <c r="F44" s="25" t="n"/>
+      <c r="G44" s="25" t="n"/>
+      <c r="H44" s="25" t="n"/>
+      <c r="I44" s="25" t="n"/>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="25" t="n"/>
+      <c r="L44" s="26" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="11" t="inlineStr">
@@ -8283,6 +8716,7 @@
       </c>
       <c r="K45" s="13">
         <f>ROUND(F45*G45, 2)</f>
+        <v/>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
@@ -8324,6 +8758,7 @@
       </c>
       <c r="K46" s="13">
         <f>ROUND(F46*G46, 2)</f>
+        <v/>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
@@ -8365,6 +8800,7 @@
       </c>
       <c r="K47" s="13">
         <f>ROUND(F47, 0)</f>
+        <v/>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
@@ -8406,6 +8842,7 @@
       </c>
       <c r="K48" s="13">
         <f>ROUND(F48*G48, 2)</f>
+        <v/>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
@@ -8447,6 +8884,7 @@
       </c>
       <c r="K49" s="13">
         <f>ROUND(F49*G49, 2)</f>
+        <v/>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
@@ -8488,6 +8926,7 @@
       </c>
       <c r="K50" s="13">
         <f>ROUND(F50*G50, 0)</f>
+        <v/>
       </c>
       <c r="L50" s="12" t="inlineStr">
         <is>
@@ -8502,15 +8941,16 @@
           <t>Cộng Số lượng Hè gang thu nước:</t>
         </is>
       </c>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="17" t="n"/>
-      <c r="F51" s="17" t="n"/>
-      <c r="G51" s="17" t="n"/>
-      <c r="H51" s="17" t="n"/>
-      <c r="I51" s="17" t="n"/>
-      <c r="J51" s="17" t="n"/>
+      <c r="D51" s="25" t="n"/>
+      <c r="E51" s="25" t="n"/>
+      <c r="F51" s="25" t="n"/>
+      <c r="G51" s="25" t="n"/>
+      <c r="H51" s="25" t="n"/>
+      <c r="I51" s="25" t="n"/>
+      <c r="J51" s="26" t="n"/>
       <c r="K51" s="19">
-        <f>F45</f>
+        <f>ROUND(K45/16.55, 0)</f>
+        <v/>
       </c>
       <c r="L51" s="20" t="inlineStr">
         <is>
@@ -8518,7 +8958,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="I53" s="21" t="inlineStr">
         <is>
@@ -8527,6 +8966,7 @@
       </c>
       <c r="J53" s="22">
         <f>K15</f>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -8537,6 +8977,7 @@
       </c>
       <c r="J54" s="22">
         <f>K24</f>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -8547,6 +8988,7 @@
       </c>
       <c r="J55" s="22">
         <f>(K9+K13+K21)/1000</f>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -8557,6 +8999,7 @@
       </c>
       <c r="J56" s="22">
         <f>K36</f>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -8567,6 +9010,7 @@
       </c>
       <c r="J57" s="22">
         <f>K43</f>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -8577,6 +9021,7 @@
       </c>
       <c r="J58" s="22">
         <f>K51</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -8604,8 +9049,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:L39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="99" customWidth="1" min="2" max="2"/>
@@ -8621,7 +9066,6 @@
     <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -8636,7 +9080,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -8700,16 +9143,16 @@
           <t>1. TỨ NÓN, KÈ ĐÁ HỘC XÂY VỮA VXM M100 &amp; CHÂN KHAY (MỐ M1, M2)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="11" t="inlineStr">
@@ -8886,13 +9329,13 @@
           <t>Cộng Đá hộc xây vữa VXM M100 kè tứ nón:</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="n"/>
-      <c r="I11" s="17" t="n"/>
-      <c r="J11" s="17" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
+      <c r="J11" s="26" t="n"/>
       <c r="K11" s="19">
         <f>K7+K8</f>
         <v/>
@@ -8909,16 +9352,16 @@
           <t>2. TƯỜNG CHẮN BÊ TÔNG TRỌNG LỰC C15 (MỐ M2)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="25" t="n"/>
+      <c r="L12" s="26" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="11" t="inlineStr">
@@ -9179,13 +9622,13 @@
           <t>Cộng Bê tông Tường chắn C15:</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="n"/>
-      <c r="I19" s="17" t="n"/>
-      <c r="J19" s="17" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
+      <c r="J19" s="26" t="n"/>
       <c r="K19" s="19">
         <f>K13</f>
         <v/>
@@ -9202,16 +9645,16 @@
           <t>3. KẾT CẤU ÁO ĐƯỜNG VUỐT NỐI 10M ĐẦU CẦU (MỐ M1 &amp; M2, TỔNG S=387.97M²)</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="26" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="11" t="inlineStr">
@@ -9598,13 +10041,13 @@
           <t>Cộng Diện tích Áo đường vuốt nối 10m đầu cầu:</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="17" t="n"/>
-      <c r="J30" s="17" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="26" t="n"/>
       <c r="K30" s="19">
         <f>K21</f>
         <v/>
@@ -9621,16 +10064,16 @@
           <t>4. VẬT LIỆU DẠNG HẠT THOÁT NƯỚC GIẢM TẢI ĐẮP LÒNG MỐ K98</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="10" t="n"/>
+      <c r="C31" s="25" t="n"/>
+      <c r="D31" s="25" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="25" t="n"/>
+      <c r="L31" s="26" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
@@ -9723,13 +10166,13 @@
           <t>Cộng Vật liệu hạt đắp lòng mố K98:</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="n"/>
-      <c r="F34" s="17" t="n"/>
-      <c r="G34" s="17" t="n"/>
-      <c r="H34" s="17" t="n"/>
-      <c r="I34" s="17" t="n"/>
-      <c r="J34" s="17" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="25" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="26" t="n"/>
       <c r="K34" s="19">
         <f>SUM(K32:K33)</f>
         <v/>
@@ -9740,7 +10183,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="I36" s="21" t="inlineStr">
         <is>
@@ -9806,8 +10248,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:L34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="94" customWidth="1" min="2" max="2"/>
@@ -9823,7 +10265,6 @@
     <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -9838,7 +10279,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -9902,16 +10342,16 @@
           <t>1. BỆ ĐÚC DẦM SUPER-T 38.2M TẠI BÃI ĐÚC (04 BỆ ĐÚC)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="11" t="inlineStr">
@@ -10214,13 +10654,13 @@
           <t>Cộng Bê tông Bệ đúc dầm C20:</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="17" t="n"/>
-      <c r="J14" s="17" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="26" t="n"/>
       <c r="K14" s="19">
         <f>K10</f>
         <v/>
@@ -10237,16 +10677,16 @@
           <t>2. ĐƯỜNG CÔNG VỤ TIẾP CẬN THI CÔNG DCV6 &amp; DCV6A</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
-      <c r="I15" s="10" t="n"/>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="10" t="n"/>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="25" t="n"/>
+      <c r="L15" s="26" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="11" t="inlineStr">
@@ -10465,13 +10905,13 @@
           <t>Cộng Khối lượng Đào nền đường công vụ:</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="17" t="n"/>
-      <c r="J21" s="17" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
+      <c r="J21" s="26" t="n"/>
       <c r="K21" s="19">
         <f>K16+K19</f>
         <v/>
@@ -10488,16 +10928,16 @@
           <t>3. GIÁ LAO DẦM 130T &amp; HỆ RAY LAO DẦM P43</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="26" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="11" t="inlineStr">
@@ -10716,13 +11156,13 @@
           <t>Cộng Kết cấu thép Lao dầm (Tấn):</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="17" t="n"/>
-      <c r="J28" s="17" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="26" t="n"/>
       <c r="K28" s="19">
         <f>SUM(K23:K25)</f>
         <v/>
@@ -10739,16 +11179,16 @@
           <t>4. HỆ ĐÀ GIÁO XÀ MŨ &amp; SÀN CÔNG TÁC MỐ TRỤ</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="10" t="n"/>
-      <c r="K29" s="10" t="n"/>
-      <c r="L29" s="10" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="25" t="n"/>
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="25" t="n"/>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="25" t="n"/>
+      <c r="L29" s="26" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
@@ -10925,13 +11365,13 @@
           <t>Cộng Thép đà giáo sàn công tác (Tấn):</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="n"/>
-      <c r="F34" s="17" t="n"/>
-      <c r="G34" s="17" t="n"/>
-      <c r="H34" s="17" t="n"/>
-      <c r="I34" s="17" t="n"/>
-      <c r="J34" s="17" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="25" t="n"/>
+      <c r="F34" s="25" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="26" t="n"/>
       <c r="K34" s="19">
         <f>SUM(K30:K33)</f>
         <v/>
@@ -10963,8 +11403,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="B2:H47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="94" customWidth="1" min="2" max="2"/>
@@ -10976,7 +11416,6 @@
     <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -10991,7 +11430,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="8" t="inlineStr">
         <is>
@@ -11035,12 +11473,12 @@
           <t>A. PHẦN I: KẾT CẤU PHẦN TRÊN (SUPERSTRUCTURE)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="11" t="inlineStr">
@@ -11070,6 +11508,7 @@
       </c>
       <c r="G7" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K11</f>
+        <v/>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
@@ -11105,6 +11544,7 @@
       </c>
       <c r="G8" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K16</f>
+        <v/>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
@@ -11140,6 +11580,7 @@
       </c>
       <c r="G9" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K21</f>
+        <v/>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
@@ -11175,6 +11616,7 @@
       </c>
       <c r="G10" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K27</f>
+        <v/>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -11210,6 +11652,7 @@
       </c>
       <c r="G11" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K34</f>
+        <v/>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -11245,6 +11688,7 @@
       </c>
       <c r="G12" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K43</f>
+        <v/>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
@@ -11280,6 +11724,7 @@
       </c>
       <c r="G13" s="13">
         <f>('01_DIEN_GIAI_SUPER_T'!K31+'01_DIEN_GIAI_SUPER_T'!K41)/1000</f>
+        <v/>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
@@ -11315,6 +11760,7 @@
       </c>
       <c r="G14" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K48</f>
+        <v/>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
@@ -11350,6 +11796,7 @@
       </c>
       <c r="G15" s="13">
         <f>'01_DIEN_GIAI_SUPER_T'!K53</f>
+        <v/>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
@@ -11363,12 +11810,12 @@
           <t>B. PHẦN II: KẾT CẤU PHẦN DƯỚI (SUBSTRUCTURE)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="26" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="11" t="inlineStr">
@@ -11398,6 +11845,7 @@
       </c>
       <c r="G17" s="13">
         <f>'02_DIEN_GIAI_HA_BO'!K17</f>
+        <v/>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
@@ -11433,6 +11881,7 @@
       </c>
       <c r="G18" s="13">
         <f>'02_DIEN_GIAI_HA_BO'!K15</f>
+        <v/>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
@@ -11468,6 +11917,7 @@
       </c>
       <c r="G19" s="13">
         <f>'02_DIEN_GIAI_HA_BO'!K29</f>
+        <v/>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
@@ -11503,6 +11953,7 @@
       </c>
       <c r="G20" s="13">
         <f>'02_DIEN_GIAI_HA_BO'!K27</f>
+        <v/>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
@@ -11538,6 +11989,7 @@
       </c>
       <c r="G21" s="13">
         <f>'02_DIEN_GIAI_HA_BO'!K46</f>
+        <v/>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
@@ -11573,6 +12025,7 @@
       </c>
       <c r="G22" s="13">
         <f>'02_DIEN_GIAI_HA_BO'!K41</f>
+        <v/>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
@@ -11586,12 +12039,12 @@
           <t>C. PHẦN III: KẾT CẤU PHỤ TRỢ (MISCELLANEOUS)</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+      <c r="H23" s="26" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
@@ -11621,6 +12074,7 @@
       </c>
       <c r="G24" s="13">
         <f>'03_DIEN_GIAI_PHU_TRO'!K15</f>
+        <v/>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
@@ -11656,6 +12110,7 @@
       </c>
       <c r="G25" s="13">
         <f>'03_DIEN_GIAI_PHU_TRO'!K24</f>
+        <v/>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
@@ -11691,6 +12146,7 @@
       </c>
       <c r="G26" s="13">
         <f>('03_DIEN_GIAI_PHU_TRO'!K9+'03_DIEN_GIAI_PHU_TRO'!K13+'03_DIEN_GIAI_PHU_TRO'!K21)/1000</f>
+        <v/>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
@@ -11726,6 +12182,7 @@
       </c>
       <c r="G27" s="13">
         <f>'03_DIEN_GIAI_PHU_TRO'!K36</f>
+        <v/>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
@@ -11761,6 +12218,7 @@
       </c>
       <c r="G28" s="13">
         <f>'03_DIEN_GIAI_PHU_TRO'!K43</f>
+        <v/>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
@@ -11796,6 +12254,7 @@
       </c>
       <c r="G29" s="13">
         <f>'03_DIEN_GIAI_PHU_TRO'!K51</f>
+        <v/>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
@@ -11809,12 +12268,12 @@
           <t>D. PHẦN IV: ĐƯỜNG SAU MỐ, TỨ NÓN &amp; GIA CỐ</t>
         </is>
       </c>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="11" t="inlineStr">
@@ -11844,6 +12303,7 @@
       </c>
       <c r="G31" s="13">
         <f>'04_DIEN_GIAI_DUONG_TU_NON'!K11</f>
+        <v/>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
@@ -11879,6 +12339,7 @@
       </c>
       <c r="G32" s="13">
         <f>'04_DIEN_GIAI_DUONG_TU_NON'!K19</f>
+        <v/>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
@@ -11914,6 +12375,7 @@
       </c>
       <c r="G33" s="13">
         <f>'04_DIEN_GIAI_DUONG_TU_NON'!K30</f>
+        <v/>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
@@ -11949,6 +12411,7 @@
       </c>
       <c r="G34" s="13">
         <f>'04_DIEN_GIAI_DUONG_TU_NON'!K34</f>
+        <v/>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
@@ -11962,12 +12425,12 @@
           <t>E. PHẦN V: BIỆN PHÁP THI CÔNG &amp; PHỤ TRỢ CÔNG TRƯỜNG</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
+      <c r="C35" s="25" t="n"/>
+      <c r="D35" s="25" t="n"/>
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="25" t="n"/>
+      <c r="G35" s="25" t="n"/>
+      <c r="H35" s="26" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="11" t="inlineStr">
@@ -12032,6 +12495,7 @@
       </c>
       <c r="G37" s="13">
         <f>'05_DIEN_GIAI_BPTC_CON'!K21</f>
+        <v/>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
@@ -12067,6 +12531,7 @@
       </c>
       <c r="G38" s="13">
         <f>'05_DIEN_GIAI_BPTC_CON'!K28</f>
+        <v/>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
@@ -12074,12 +12539,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
     <row r="45">
       <c r="F45" s="23" t="inlineStr">
         <is>
@@ -12088,6 +12547,7 @@
       </c>
       <c r="G45" s="24">
         <f>G7+G11+G12+G14+G17+G19+G21+G24+G25+G32</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -12098,6 +12558,7 @@
       </c>
       <c r="G46" s="24">
         <f>G9+G13+G18+G20+G22+G26</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -12108,6 +12569,7 @@
       </c>
       <c r="G47" s="24">
         <f>G10+'02_DIEN_GIAI_HA_BO'!K16+'02_DIEN_GIAI_HA_BO'!K28+'03_DIEN_GIAI_PHU_TRO'!K10+'03_DIEN_GIAI_PHU_TRO'!K14+'03_DIEN_GIAI_PHU_TRO'!K22+'04_DIEN_GIAI_DUONG_TU_NON'!K14</f>
+        <v/>
       </c>
     </row>
   </sheetData>
